--- a/teacher/tracker-as-applied.xlsx
+++ b/teacher/tracker-as-applied.xlsx
@@ -156,7 +156,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
     <dxf>
       <font>
         <b val="1"/>
@@ -187,6 +187,42 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="001B998B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC0392B"/>
+          <bgColor rgb="FFC0392B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4A93F"/>
+          <bgColor rgb="FFF4A93F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1B998B"/>
+          <bgColor rgb="FF1B998B"/>
         </patternFill>
       </fill>
     </dxf>
@@ -840,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1137,13 +1173,13 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:E27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1162,7 +1198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1489,13 +1525,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1514,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1811,13 +1847,13 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:E27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1836,7 +1872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2163,13 +2199,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2188,7 +2224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2515,13 +2551,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2540,7 +2576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2867,13 +2903,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2892,7 +2928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3159,13 +3195,13 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:D27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3184,7 +3220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3451,13 +3487,13 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:D27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3476,7 +3512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3743,13 +3779,13 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:D27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3768,7 +3804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4065,13 +4101,13 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:E27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4090,7 +4126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4387,13 +4423,13 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:E27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
